--- a/business_surveys/041_process_automation_insight_survey--business_surveys.xlsx
+++ b/business_surveys/041_process_automation_insight_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>workflow_goal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the primary goal of your workflow?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the main objective of your workflow.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,110 +547,130 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>number_of_workflows</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what-is-the-primary-goal-of-your-workflow</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How many workflows do you have?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the number of workflows.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1_answer</t>
+          <t>tools_used</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what-is-the-primary-goal-of-your-workflow</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Which tools are you currently using for your workflows?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please list the tools used.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>benefit_of_automation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how-many-workflows-do-you-have</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the primary benefit of your automated workflows?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please describe the main advantage.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2_answer</t>
+          <t>survey_schedule</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how-many-workflows-do-you-have</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>On what schedule is this survey expected to be completed?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide the expected completion time.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>survey_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>which-tools-are-you-currently-using</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What would be the best time to conduct this survey according to your perspective?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide the best time.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,84 +682,100 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3_answer</t>
+          <t>similar_surveys</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>which-tools-are-you-currently-using</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Have you conducted similar surveys in the past?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please answer yes or no.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>recent_survey_url</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what-is-the-primary-benefit-of-your-automated-workflows</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the URL of the survey you have conducted most recently?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide the URL.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_4_answer</t>
+          <t>participate_in_future</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what-is-the-primary-benefit-of-your-automated-workflows</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you want to participate in future surveys?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please answer yes or no.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>on-what-schedule-is-this-survey-be-expected-to-be-completed</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you have any comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,43 +785,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5_answer</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>on-what-schedule-is-this-survey-be-expected-to-be-completed</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your contact email address?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your email address.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>follow_up_question_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what-would-be-the-best-time-to-conduct-this-survey-according-to-your-perspective</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Follow-up question 1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please answer according to your understanding.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,297 +839,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_6_answer</t>
+          <t>contact_answer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what-would-be-the-best-time-to-conduct-this-survey-according-to-your-perspective</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is your contact information?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any additional contact information.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>have-you-conducted-similar-surveys-in-the-past</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_7_answer</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>have-you-conducted-similar-surveys-in-the-past</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>if-so-please-share-the-url-of-the-survey-you-have-conducted-most-recently</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_8_answer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>if-so-please-share-the-url-of-the-survey-you-have-conducted-most-recently</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>do-you-want-to-participate-in-the-future</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_9_answer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>do-you-want-to-participate-in-the-future</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>do-you-have-any-comments-or-suggestions</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_10_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>do-you-have-any-comments-or-suggestions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_answer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up_question_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow-up-question-1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_answer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow-up-question-1-answer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +874,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,714 +902,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tool1</t>
+          <t>zapier</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tool1</t>
+          <t>Zapier</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tool2</t>
+          <t>automata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tool2</t>
+          <t>Automata</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tool3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tool3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_3_answer_choices</t>
+          <t>benefit_of_automation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tool1</t>
+          <t>increased_efficiency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tool1</t>
+          <t>Increased efficiency</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_answer_choices</t>
+          <t>benefit_of_automation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tool2</t>
+          <t>improved_accuracy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tool2</t>
+          <t>Improved accuracy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_answer_choices</t>
+          <t>benefit_of_automation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tool3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tool3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>survey_schedule_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>asap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>survey_schedule_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>within_a_few_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Within a few days</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>survey_schedule_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>within_a_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Within a week</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_4_answer_choices</t>
+          <t>survey_time_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>now</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Now</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_4_answer_choices</t>
+          <t>survey_time_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>later_today</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Later today</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_4_answer_choices</t>
+          <t>survey_time_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>tomorrow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Tomorrow</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>similar_surveys_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>similar_surveys_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>participate_in_future_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_5_answer_choices</t>
+          <t>participate_in_future_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_5_answer_choices</t>
+          <t>follow_up_question_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_5_answer_choices</t>
+          <t>follow_up_question_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_6_answer_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_6_answer_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_6_answer_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_7_answer_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_7_answer_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_7_answer_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_9_answer_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_9_answer_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_9_answer_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_answer_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_answer_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>follow_up_question_1_answer_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>False</t>
         </is>
       </c>
     </row>
